--- a/data/mview.xlsx
+++ b/data/mview.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\連訊\股市實驗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\stock_projects\stockportal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784064E4-2493-4EC9-B13A-10AE7D239892}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4478EB1-A527-4113-B3A5-C946351BEDB3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5103" uniqueCount="2755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5103" uniqueCount="2756">
   <si>
     <t>公司代號</t>
   </si>
@@ -8285,6 +8285,10 @@
   </si>
   <si>
     <t>總結說明</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -8844,7 +8848,7 @@
         <v>56</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>2755</v>
       </c>
       <c r="H2">
         <v>0</v>
